--- a/ecommerse_automation_practice/project_documents.xlsx
+++ b/ecommerse_automation_practice/project_documents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\eclipse_coding_projects\selenium_automation\ecommerse_automation_practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE9A4D8-5055-4C16-994D-37B71857DB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936FBE0A-ED14-4F4E-9657-1486EBE3A5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,26 @@
     <sheet name="SearchProductsPage" sheetId="3" r:id="rId3"/>
     <sheet name="WishlistPage" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>title</t>
   </si>
@@ -46,6 +55,12 @@
   </si>
   <si>
     <t>http://localhost:5173/homepage</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Shop | ECODERS</t>
   </si>
 </sst>
 </file>
@@ -90,9 +105,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -374,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" customWidth="1"/>
@@ -383,7 +399,7 @@
     <col min="4" max="4" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -391,7 +407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -403,6 +419,20 @@
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="E2">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D4" s="2">
+        <v>49290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <f>(E4+E5+E6+E7+E8+E9+E10+E11)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -416,9 +446,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DECF4EDD-40F8-4043-B6B3-4E5FD85806A7}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
